--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -7,9 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weather" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tournament" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Players" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CourseFit" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Weather" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="GitHub_Setup" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,109 +420,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>max_temp</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>precipitation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>wind_speed</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="C2" t="n">
-        <v>56</v>
-      </c>
-      <c r="D2" t="n">
-        <v>11.7</v>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-26 22:43</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="C3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D3" t="n">
-        <v>13.1</v>
+          <t>Tournament</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Current PGA Event</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="C4" t="n">
-        <v>47</v>
-      </c>
-      <c r="D4" t="n">
-        <v>12.2</v>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Course updates weekly/manual</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22.4</v>
+          <t>Course Style</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Major-style test</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>Players in Model</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>67</v>
-      </c>
-      <c r="D6" t="n">
-        <v>18.1</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Top Projected Player</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Scottie Scheffler</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Average Wind MPH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Average Rain Chance</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Model Note</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Free starter model using manual player ratings, course fit, and weather.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -531,125 +548,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>tournament</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>world_rank</t>
+          <t>course</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>projected_score</t>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>course_style</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>driving_importance</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>iron_importance</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>short_game_importance</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>putting_importance</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scottie Scheffler</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+          <t>Current PGA Event</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Course updates weekly/manual</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>98</v>
+        <v>33.502</v>
       </c>
       <c r="D2" t="n">
-        <v>98.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Rory McIlroy</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>95</v>
-      </c>
-      <c r="D3" t="n">
-        <v>95.90000000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Xander Schauffele</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>93</v>
-      </c>
-      <c r="D4" t="n">
-        <v>94.19999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Collin Morikawa</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>91</v>
-      </c>
-      <c r="D5" t="n">
-        <v>92.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ludvig Aberg</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>90</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Justin Thomas</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>89</v>
-      </c>
-      <c r="D7" t="n">
-        <v>90.5</v>
+        <v>-82.0228</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Major-style test</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -663,54 +644,5642 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>World Rank</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Base Rating</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Driving Rating</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Iron Rating</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Putting Rating</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last Updated</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-26 22:34</t>
-        </is>
+          <t>Scottie Scheffler</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tournament</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Current PGA Event</t>
-        </is>
+          <t>Rory McIlroy</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Xander Schauffele</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D4" t="n">
+        <v>94</v>
+      </c>
+      <c r="E4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Collin Morikawa</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>93</v>
+      </c>
+      <c r="D5" t="n">
+        <v>91</v>
+      </c>
+      <c r="E5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F5" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ludvig Aberg</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>92</v>
+      </c>
+      <c r="D6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Viktor Hovland</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" t="n">
+        <v>88</v>
+      </c>
+      <c r="F7" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Patrick Cantlay</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>88</v>
+      </c>
+      <c r="E8" t="n">
+        <v>91</v>
+      </c>
+      <c r="F8" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wyndham Clark</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D9" t="n">
+        <v>92</v>
+      </c>
+      <c r="E9" t="n">
+        <v>84</v>
+      </c>
+      <c r="F9" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hideki Matsuyama</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>88</v>
+      </c>
+      <c r="D10" t="n">
+        <v>87</v>
+      </c>
+      <c r="E10" t="n">
+        <v>90</v>
+      </c>
+      <c r="F10" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tommy Fleetwood</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>88</v>
+      </c>
+      <c r="D11" t="n">
+        <v>86</v>
+      </c>
+      <c r="E11" t="n">
+        <v>91</v>
+      </c>
+      <c r="F11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Max Homa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>87</v>
+      </c>
+      <c r="D12" t="n">
+        <v>85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Justin Thomas</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>86</v>
+      </c>
+      <c r="D13" t="n">
+        <v>87</v>
+      </c>
+      <c r="E13" t="n">
+        <v>84</v>
+      </c>
+      <c r="F13" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jordan Spieth</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E14" t="n">
+        <v>82</v>
+      </c>
+      <c r="F14" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sam Burns</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="n">
+        <v>84</v>
+      </c>
+      <c r="D15" t="n">
+        <v>86</v>
+      </c>
+      <c r="E15" t="n">
+        <v>80</v>
+      </c>
+      <c r="F15" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tony Finau</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>84</v>
+      </c>
+      <c r="D16" t="n">
+        <v>88</v>
+      </c>
+      <c r="E16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cameron Young</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>83</v>
+      </c>
+      <c r="D17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E17" t="n">
+        <v>78</v>
+      </c>
+      <c r="F17" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sahith Theegala</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>83</v>
+      </c>
+      <c r="D18" t="n">
+        <v>84</v>
+      </c>
+      <c r="E18" t="n">
+        <v>80</v>
+      </c>
+      <c r="F18" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Russell Henley</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="n">
+        <v>82</v>
+      </c>
+      <c r="D19" t="n">
+        <v>78</v>
+      </c>
+      <c r="E19" t="n">
+        <v>88</v>
+      </c>
+      <c r="F19" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Matt Fitzpatrick</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="n">
+        <v>82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>79</v>
+      </c>
+      <c r="E20" t="n">
+        <v>86</v>
+      </c>
+      <c r="F20" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Keegan Bradley</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="n">
+        <v>81</v>
+      </c>
+      <c r="D21" t="n">
+        <v>82</v>
+      </c>
+      <c r="E21" t="n">
+        <v>84</v>
+      </c>
+      <c r="F21" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brian Harman</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="n">
+        <v>81</v>
+      </c>
+      <c r="D22" t="n">
+        <v>76</v>
+      </c>
+      <c r="E22" t="n">
+        <v>87</v>
+      </c>
+      <c r="F22" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jason Day</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>80</v>
+      </c>
+      <c r="D23" t="n">
+        <v>78</v>
+      </c>
+      <c r="E23" t="n">
+        <v>82</v>
+      </c>
+      <c r="F23" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sepp Straka</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>80</v>
+      </c>
+      <c r="D24" t="n">
+        <v>81</v>
+      </c>
+      <c r="E24" t="n">
+        <v>83</v>
+      </c>
+      <c r="F24" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Min Woo Lee</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="n">
+        <v>79</v>
+      </c>
+      <c r="D25" t="n">
+        <v>86</v>
+      </c>
+      <c r="E25" t="n">
+        <v>77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Akshay Bhatia</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>79</v>
+      </c>
+      <c r="D26" t="n">
+        <v>80</v>
+      </c>
+      <c r="E26" t="n">
+        <v>82</v>
+      </c>
+      <c r="F26" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Corey Conners</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="n">
+        <v>78</v>
+      </c>
+      <c r="D27" t="n">
+        <v>79</v>
+      </c>
+      <c r="E27" t="n">
+        <v>86</v>
+      </c>
+      <c r="F27" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Adam Scott</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="n">
+        <v>78</v>
+      </c>
+      <c r="D28" t="n">
+        <v>81</v>
+      </c>
+      <c r="E28" t="n">
+        <v>80</v>
+      </c>
+      <c r="F28" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Si Woo Kim</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="n">
+        <v>77</v>
+      </c>
+      <c r="D29" t="n">
+        <v>79</v>
+      </c>
+      <c r="E29" t="n">
+        <v>81</v>
+      </c>
+      <c r="F29" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Shane Lowry</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="n">
+        <v>77</v>
+      </c>
+      <c r="D30" t="n">
+        <v>75</v>
+      </c>
+      <c r="E30" t="n">
+        <v>84</v>
+      </c>
+      <c r="F30" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Rickie Fowler</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>76</v>
+      </c>
+      <c r="D31" t="n">
+        <v>78</v>
+      </c>
+      <c r="E31" t="n">
+        <v>80</v>
+      </c>
+      <c r="F31" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Will Zalatoris</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="n">
+        <v>76</v>
+      </c>
+      <c r="D32" t="n">
+        <v>83</v>
+      </c>
+      <c r="E32" t="n">
+        <v>79</v>
+      </c>
+      <c r="F32" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Denny McCarthy</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="n">
+        <v>75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>72</v>
+      </c>
+      <c r="E33" t="n">
+        <v>78</v>
+      </c>
+      <c r="F33" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tom Kim</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="n">
+        <v>75</v>
+      </c>
+      <c r="D34" t="n">
+        <v>74</v>
+      </c>
+      <c r="E34" t="n">
+        <v>83</v>
+      </c>
+      <c r="F34" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Eric Cole</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="n">
+        <v>74</v>
+      </c>
+      <c r="D35" t="n">
+        <v>73</v>
+      </c>
+      <c r="E35" t="n">
+        <v>79</v>
+      </c>
+      <c r="F35" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>J.T. Poston</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="n">
+        <v>74</v>
+      </c>
+      <c r="D36" t="n">
+        <v>72</v>
+      </c>
+      <c r="E36" t="n">
+        <v>81</v>
+      </c>
+      <c r="F36" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chris Kirk</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="n">
+        <v>73</v>
+      </c>
+      <c r="D37" t="n">
+        <v>74</v>
+      </c>
+      <c r="E37" t="n">
+        <v>80</v>
+      </c>
+      <c r="F37" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Byeong Hun An</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="n">
+        <v>73</v>
+      </c>
+      <c r="D38" t="n">
+        <v>82</v>
+      </c>
+      <c r="E38" t="n">
+        <v>75</v>
+      </c>
+      <c r="F38" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Harris English</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="n">
+        <v>72</v>
+      </c>
+      <c r="D39" t="n">
+        <v>75</v>
+      </c>
+      <c r="E39" t="n">
+        <v>79</v>
+      </c>
+      <c r="F39" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lucas Glover</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="n">
+        <v>72</v>
+      </c>
+      <c r="D40" t="n">
+        <v>76</v>
+      </c>
+      <c r="E40" t="n">
+        <v>82</v>
+      </c>
+      <c r="F40" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Maverick McNealy</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="n">
+        <v>71</v>
+      </c>
+      <c r="D41" t="n">
+        <v>73</v>
+      </c>
+      <c r="E41" t="n">
+        <v>78</v>
+      </c>
+      <c r="F41" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Taylor Moore</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="n">
+        <v>71</v>
+      </c>
+      <c r="D42" t="n">
+        <v>75</v>
+      </c>
+      <c r="E42" t="n">
+        <v>76</v>
+      </c>
+      <c r="F42" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kurt Kitayama</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="n">
+        <v>70</v>
+      </c>
+      <c r="D43" t="n">
+        <v>79</v>
+      </c>
+      <c r="E43" t="n">
+        <v>74</v>
+      </c>
+      <c r="F43" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Nicolai Hojgaard</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="n">
+        <v>70</v>
+      </c>
+      <c r="D44" t="n">
+        <v>82</v>
+      </c>
+      <c r="E44" t="n">
+        <v>73</v>
+      </c>
+      <c r="F44" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cam Davis</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="n">
+        <v>69</v>
+      </c>
+      <c r="D45" t="n">
+        <v>78</v>
+      </c>
+      <c r="E45" t="n">
+        <v>74</v>
+      </c>
+      <c r="F45" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Adam Hadwin</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="n">
+        <v>69</v>
+      </c>
+      <c r="D46" t="n">
+        <v>72</v>
+      </c>
+      <c r="E46" t="n">
+        <v>80</v>
+      </c>
+      <c r="F46" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Nick Taylor</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="n">
+        <v>68</v>
+      </c>
+      <c r="D47" t="n">
+        <v>71</v>
+      </c>
+      <c r="E47" t="n">
+        <v>79</v>
+      </c>
+      <c r="F47" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Keith Mitchell</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="n">
+        <v>68</v>
+      </c>
+      <c r="D48" t="n">
+        <v>83</v>
+      </c>
+      <c r="E48" t="n">
+        <v>72</v>
+      </c>
+      <c r="F48" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Beau Hossler</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="n">
+        <v>67</v>
+      </c>
+      <c r="D49" t="n">
+        <v>73</v>
+      </c>
+      <c r="E49" t="n">
+        <v>76</v>
+      </c>
+      <c r="F49" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Andrew Putnam</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="n">
+        <v>67</v>
+      </c>
+      <c r="D50" t="n">
+        <v>68</v>
+      </c>
+      <c r="E50" t="n">
+        <v>81</v>
+      </c>
+      <c r="F50" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Davis Thompson</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="n">
+        <v>66</v>
+      </c>
+      <c r="D51" t="n">
+        <v>76</v>
+      </c>
+      <c r="E51" t="n">
+        <v>75</v>
+      </c>
+      <c r="F51" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Austin Eckroat</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="n">
+        <v>66</v>
+      </c>
+      <c r="D52" t="n">
+        <v>74</v>
+      </c>
+      <c r="E52" t="n">
+        <v>77</v>
+      </c>
+      <c r="F52" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jake Knapp</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="n">
+        <v>65</v>
+      </c>
+      <c r="D53" t="n">
+        <v>81</v>
+      </c>
+      <c r="E53" t="n">
+        <v>70</v>
+      </c>
+      <c r="F53" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ben Griffin</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="n">
+        <v>65</v>
+      </c>
+      <c r="D54" t="n">
+        <v>72</v>
+      </c>
+      <c r="E54" t="n">
+        <v>78</v>
+      </c>
+      <c r="F54" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Taylor Pendrith</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="n">
+        <v>64</v>
+      </c>
+      <c r="D55" t="n">
+        <v>82</v>
+      </c>
+      <c r="E55" t="n">
+        <v>71</v>
+      </c>
+      <c r="F55" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Alex Noren</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="n">
+        <v>64</v>
+      </c>
+      <c r="D56" t="n">
+        <v>70</v>
+      </c>
+      <c r="E56" t="n">
+        <v>82</v>
+      </c>
+      <c r="F56" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Emiliano Grillo</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="n">
+        <v>63</v>
+      </c>
+      <c r="D57" t="n">
+        <v>72</v>
+      </c>
+      <c r="E57" t="n">
+        <v>79</v>
+      </c>
+      <c r="F57" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Brendon Todd</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="n">
+        <v>63</v>
+      </c>
+      <c r="D58" t="n">
+        <v>65</v>
+      </c>
+      <c r="E58" t="n">
+        <v>78</v>
+      </c>
+      <c r="F58" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gary Woodland</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="n">
+        <v>62</v>
+      </c>
+      <c r="D59" t="n">
+        <v>78</v>
+      </c>
+      <c r="E59" t="n">
+        <v>70</v>
+      </c>
+      <c r="F59" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Billy Horschel</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="n">
+        <v>62</v>
+      </c>
+      <c r="D60" t="n">
+        <v>71</v>
+      </c>
+      <c r="E60" t="n">
+        <v>77</v>
+      </c>
+      <c r="F60" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Christiaan Bezuidenhout</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="n">
+        <v>61</v>
+      </c>
+      <c r="D61" t="n">
+        <v>68</v>
+      </c>
+      <c r="E61" t="n">
+        <v>80</v>
+      </c>
+      <c r="F61" t="n">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>World Rank</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Base Rating</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Driving Rating</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Iron Rating</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Putting Rating</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Course Fit Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Scottie Scheffler</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" t="n">
+        <v>94</v>
+      </c>
+      <c r="G2" t="n">
+        <v>95.65000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rory McIlroy</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>91</v>
+      </c>
+      <c r="G3" t="n">
+        <v>93.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Xander Schauffele</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D4" t="n">
+        <v>94</v>
+      </c>
+      <c r="E4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G4" t="n">
+        <v>92.69999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Collin Morikawa</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>93</v>
+      </c>
+      <c r="D5" t="n">
+        <v>91</v>
+      </c>
+      <c r="E5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F5" t="n">
+        <v>88</v>
+      </c>
+      <c r="G5" t="n">
+        <v>92.54999999999998</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ludvig Aberg</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>92</v>
+      </c>
+      <c r="D6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87</v>
+      </c>
+      <c r="G6" t="n">
+        <v>90.80000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Patrick Cantlay</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="n">
+        <v>88</v>
+      </c>
+      <c r="E7" t="n">
+        <v>91</v>
+      </c>
+      <c r="F7" t="n">
+        <v>89</v>
+      </c>
+      <c r="G7" t="n">
+        <v>89.64999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Viktor Hovland</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>91</v>
+      </c>
+      <c r="D8" t="n">
+        <v>90</v>
+      </c>
+      <c r="E8" t="n">
+        <v>88</v>
+      </c>
+      <c r="F8" t="n">
+        <v>86</v>
+      </c>
+      <c r="G8" t="n">
+        <v>88.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hideki Matsuyama</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>88</v>
+      </c>
+      <c r="D9" t="n">
+        <v>87</v>
+      </c>
+      <c r="E9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" t="n">
+        <v>85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>87.84999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tommy Fleetwood</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="n">
+        <v>88</v>
+      </c>
+      <c r="D10" t="n">
+        <v>86</v>
+      </c>
+      <c r="E10" t="n">
+        <v>91</v>
+      </c>
+      <c r="F10" t="n">
+        <v>84</v>
+      </c>
+      <c r="G10" t="n">
+        <v>87.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Wyndham Clark</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>89</v>
+      </c>
+      <c r="D11" t="n">
+        <v>92</v>
+      </c>
+      <c r="E11" t="n">
+        <v>84</v>
+      </c>
+      <c r="F11" t="n">
+        <v>86</v>
+      </c>
+      <c r="G11" t="n">
+        <v>87.39999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Max Homa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>87</v>
+      </c>
+      <c r="D12" t="n">
+        <v>85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>86</v>
+      </c>
+      <c r="G12" t="n">
+        <v>86.65000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Justin Thomas</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>86</v>
+      </c>
+      <c r="D13" t="n">
+        <v>87</v>
+      </c>
+      <c r="E13" t="n">
+        <v>84</v>
+      </c>
+      <c r="F13" t="n">
+        <v>83</v>
+      </c>
+      <c r="G13" t="n">
+        <v>84.95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jordan Spieth</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E14" t="n">
+        <v>82</v>
+      </c>
+      <c r="F14" t="n">
+        <v>90</v>
+      </c>
+      <c r="G14" t="n">
+        <v>84.45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tony Finau</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" t="n">
+        <v>84</v>
+      </c>
+      <c r="D15" t="n">
+        <v>88</v>
+      </c>
+      <c r="E15" t="n">
+        <v>82</v>
+      </c>
+      <c r="F15" t="n">
+        <v>81</v>
+      </c>
+      <c r="G15" t="n">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Russell Henley</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C16" t="n">
+        <v>82</v>
+      </c>
+      <c r="D16" t="n">
+        <v>78</v>
+      </c>
+      <c r="E16" t="n">
+        <v>88</v>
+      </c>
+      <c r="F16" t="n">
+        <v>83</v>
+      </c>
+      <c r="G16" t="n">
+        <v>83.30000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sam Burns</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>84</v>
+      </c>
+      <c r="D17" t="n">
+        <v>86</v>
+      </c>
+      <c r="E17" t="n">
+        <v>80</v>
+      </c>
+      <c r="F17" t="n">
+        <v>85</v>
+      </c>
+      <c r="G17" t="n">
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Matt Fitzpatrick</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>19</v>
+      </c>
+      <c r="C18" t="n">
+        <v>82</v>
+      </c>
+      <c r="D18" t="n">
+        <v>79</v>
+      </c>
+      <c r="E18" t="n">
+        <v>86</v>
+      </c>
+      <c r="F18" t="n">
+        <v>84</v>
+      </c>
+      <c r="G18" t="n">
+        <v>83.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sahith Theegala</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>83</v>
+      </c>
+      <c r="D19" t="n">
+        <v>84</v>
+      </c>
+      <c r="E19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F19" t="n">
+        <v>86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>82.80000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Brian Harman</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>21</v>
+      </c>
+      <c r="C20" t="n">
+        <v>81</v>
+      </c>
+      <c r="D20" t="n">
+        <v>76</v>
+      </c>
+      <c r="E20" t="n">
+        <v>87</v>
+      </c>
+      <c r="F20" t="n">
+        <v>83</v>
+      </c>
+      <c r="G20" t="n">
+        <v>82.25000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cameron Young</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>83</v>
+      </c>
+      <c r="D21" t="n">
+        <v>90</v>
+      </c>
+      <c r="E21" t="n">
+        <v>78</v>
+      </c>
+      <c r="F21" t="n">
+        <v>79</v>
+      </c>
+      <c r="G21" t="n">
+        <v>82.19999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Keegan Bradley</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="n">
+        <v>81</v>
+      </c>
+      <c r="D22" t="n">
+        <v>82</v>
+      </c>
+      <c r="E22" t="n">
+        <v>84</v>
+      </c>
+      <c r="F22" t="n">
+        <v>80</v>
+      </c>
+      <c r="G22" t="n">
+        <v>82.10000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jason Day</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>80</v>
+      </c>
+      <c r="D23" t="n">
+        <v>78</v>
+      </c>
+      <c r="E23" t="n">
+        <v>82</v>
+      </c>
+      <c r="F23" t="n">
+        <v>86</v>
+      </c>
+      <c r="G23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sepp Straka</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>80</v>
+      </c>
+      <c r="D24" t="n">
+        <v>81</v>
+      </c>
+      <c r="E24" t="n">
+        <v>83</v>
+      </c>
+      <c r="F24" t="n">
+        <v>79</v>
+      </c>
+      <c r="G24" t="n">
+        <v>81.09999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Shane Lowry</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>29</v>
+      </c>
+      <c r="C25" t="n">
+        <v>77</v>
+      </c>
+      <c r="D25" t="n">
+        <v>75</v>
+      </c>
+      <c r="E25" t="n">
+        <v>84</v>
+      </c>
+      <c r="F25" t="n">
+        <v>86</v>
+      </c>
+      <c r="G25" t="n">
+        <v>80.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Corey Conners</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>26</v>
+      </c>
+      <c r="C26" t="n">
+        <v>78</v>
+      </c>
+      <c r="D26" t="n">
+        <v>79</v>
+      </c>
+      <c r="E26" t="n">
+        <v>86</v>
+      </c>
+      <c r="F26" t="n">
+        <v>76</v>
+      </c>
+      <c r="G26" t="n">
+        <v>80.65000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Akshay Bhatia</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>79</v>
+      </c>
+      <c r="D27" t="n">
+        <v>80</v>
+      </c>
+      <c r="E27" t="n">
+        <v>82</v>
+      </c>
+      <c r="F27" t="n">
+        <v>80</v>
+      </c>
+      <c r="G27" t="n">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Min Woo Lee</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" t="n">
+        <v>79</v>
+      </c>
+      <c r="D28" t="n">
+        <v>86</v>
+      </c>
+      <c r="E28" t="n">
+        <v>77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>81</v>
+      </c>
+      <c r="G28" t="n">
+        <v>80.45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Adam Scott</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="n">
+        <v>78</v>
+      </c>
+      <c r="D29" t="n">
+        <v>81</v>
+      </c>
+      <c r="E29" t="n">
+        <v>80</v>
+      </c>
+      <c r="F29" t="n">
+        <v>82</v>
+      </c>
+      <c r="G29" t="n">
+        <v>80.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Si Woo Kim</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>77</v>
+      </c>
+      <c r="D30" t="n">
+        <v>79</v>
+      </c>
+      <c r="E30" t="n">
+        <v>81</v>
+      </c>
+      <c r="F30" t="n">
+        <v>80</v>
+      </c>
+      <c r="G30" t="n">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Rickie Fowler</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>76</v>
+      </c>
+      <c r="D31" t="n">
+        <v>78</v>
+      </c>
+      <c r="E31" t="n">
+        <v>80</v>
+      </c>
+      <c r="F31" t="n">
+        <v>82</v>
+      </c>
+      <c r="G31" t="n">
+        <v>79.10000000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tom Kim</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>33</v>
+      </c>
+      <c r="C32" t="n">
+        <v>75</v>
+      </c>
+      <c r="D32" t="n">
+        <v>74</v>
+      </c>
+      <c r="E32" t="n">
+        <v>83</v>
+      </c>
+      <c r="F32" t="n">
+        <v>81</v>
+      </c>
+      <c r="G32" t="n">
+        <v>78.75</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Denny McCarthy</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="n">
+        <v>75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>72</v>
+      </c>
+      <c r="E33" t="n">
+        <v>78</v>
+      </c>
+      <c r="F33" t="n">
+        <v>92</v>
+      </c>
+      <c r="G33" t="n">
+        <v>78.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Will Zalatoris</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>31</v>
+      </c>
+      <c r="C34" t="n">
+        <v>76</v>
+      </c>
+      <c r="D34" t="n">
+        <v>83</v>
+      </c>
+      <c r="E34" t="n">
+        <v>79</v>
+      </c>
+      <c r="F34" t="n">
+        <v>74</v>
+      </c>
+      <c r="G34" t="n">
+        <v>78.40000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>J.T. Poston</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C35" t="n">
+        <v>74</v>
+      </c>
+      <c r="D35" t="n">
+        <v>72</v>
+      </c>
+      <c r="E35" t="n">
+        <v>81</v>
+      </c>
+      <c r="F35" t="n">
+        <v>86</v>
+      </c>
+      <c r="G35" t="n">
+        <v>78.34999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Eric Cole</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="n">
+        <v>74</v>
+      </c>
+      <c r="D36" t="n">
+        <v>73</v>
+      </c>
+      <c r="E36" t="n">
+        <v>79</v>
+      </c>
+      <c r="F36" t="n">
+        <v>84</v>
+      </c>
+      <c r="G36" t="n">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chris Kirk</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="n">
+        <v>73</v>
+      </c>
+      <c r="D37" t="n">
+        <v>74</v>
+      </c>
+      <c r="E37" t="n">
+        <v>80</v>
+      </c>
+      <c r="F37" t="n">
+        <v>82</v>
+      </c>
+      <c r="G37" t="n">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Lucas Glover</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>39</v>
+      </c>
+      <c r="C38" t="n">
+        <v>72</v>
+      </c>
+      <c r="D38" t="n">
+        <v>76</v>
+      </c>
+      <c r="E38" t="n">
+        <v>82</v>
+      </c>
+      <c r="F38" t="n">
+        <v>75</v>
+      </c>
+      <c r="G38" t="n">
+        <v>77.10000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Harris English</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="n">
+        <v>72</v>
+      </c>
+      <c r="D39" t="n">
+        <v>75</v>
+      </c>
+      <c r="E39" t="n">
+        <v>79</v>
+      </c>
+      <c r="F39" t="n">
+        <v>81</v>
+      </c>
+      <c r="G39" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Byeong Hun An</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" t="n">
+        <v>73</v>
+      </c>
+      <c r="D40" t="n">
+        <v>82</v>
+      </c>
+      <c r="E40" t="n">
+        <v>75</v>
+      </c>
+      <c r="F40" t="n">
+        <v>76</v>
+      </c>
+      <c r="G40" t="n">
+        <v>76.55000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Maverick McNealy</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="n">
+        <v>71</v>
+      </c>
+      <c r="D41" t="n">
+        <v>73</v>
+      </c>
+      <c r="E41" t="n">
+        <v>78</v>
+      </c>
+      <c r="F41" t="n">
+        <v>84</v>
+      </c>
+      <c r="G41" t="n">
+        <v>76.55</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Adam Hadwin</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>45</v>
+      </c>
+      <c r="C42" t="n">
+        <v>69</v>
+      </c>
+      <c r="D42" t="n">
+        <v>72</v>
+      </c>
+      <c r="E42" t="n">
+        <v>80</v>
+      </c>
+      <c r="F42" t="n">
+        <v>82</v>
+      </c>
+      <c r="G42" t="n">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Taylor Moore</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" t="n">
+        <v>71</v>
+      </c>
+      <c r="D43" t="n">
+        <v>75</v>
+      </c>
+      <c r="E43" t="n">
+        <v>76</v>
+      </c>
+      <c r="F43" t="n">
+        <v>82</v>
+      </c>
+      <c r="G43" t="n">
+        <v>75.95</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Andrew Putnam</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>49</v>
+      </c>
+      <c r="C44" t="n">
+        <v>67</v>
+      </c>
+      <c r="D44" t="n">
+        <v>68</v>
+      </c>
+      <c r="E44" t="n">
+        <v>81</v>
+      </c>
+      <c r="F44" t="n">
+        <v>86</v>
+      </c>
+      <c r="G44" t="n">
+        <v>75.95</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Alex Noren</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>55</v>
+      </c>
+      <c r="C45" t="n">
+        <v>64</v>
+      </c>
+      <c r="D45" t="n">
+        <v>70</v>
+      </c>
+      <c r="E45" t="n">
+        <v>82</v>
+      </c>
+      <c r="F45" t="n">
+        <v>83</v>
+      </c>
+      <c r="G45" t="n">
+        <v>75.60000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Nick Taylor</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>46</v>
+      </c>
+      <c r="C46" t="n">
+        <v>68</v>
+      </c>
+      <c r="D46" t="n">
+        <v>71</v>
+      </c>
+      <c r="E46" t="n">
+        <v>79</v>
+      </c>
+      <c r="F46" t="n">
+        <v>83</v>
+      </c>
+      <c r="G46" t="n">
+        <v>75.59999999999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kurt Kitayama</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>42</v>
+      </c>
+      <c r="C47" t="n">
+        <v>70</v>
+      </c>
+      <c r="D47" t="n">
+        <v>79</v>
+      </c>
+      <c r="E47" t="n">
+        <v>74</v>
+      </c>
+      <c r="F47" t="n">
+        <v>78</v>
+      </c>
+      <c r="G47" t="n">
+        <v>75.25</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Nicolai Hojgaard</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>43</v>
+      </c>
+      <c r="C48" t="n">
+        <v>70</v>
+      </c>
+      <c r="D48" t="n">
+        <v>82</v>
+      </c>
+      <c r="E48" t="n">
+        <v>73</v>
+      </c>
+      <c r="F48" t="n">
+        <v>76</v>
+      </c>
+      <c r="G48" t="n">
+        <v>75.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cam Davis</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>44</v>
+      </c>
+      <c r="C49" t="n">
+        <v>69</v>
+      </c>
+      <c r="D49" t="n">
+        <v>78</v>
+      </c>
+      <c r="E49" t="n">
+        <v>74</v>
+      </c>
+      <c r="F49" t="n">
+        <v>80</v>
+      </c>
+      <c r="G49" t="n">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Beau Hossler</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" t="n">
+        <v>67</v>
+      </c>
+      <c r="D50" t="n">
+        <v>73</v>
+      </c>
+      <c r="E50" t="n">
+        <v>76</v>
+      </c>
+      <c r="F50" t="n">
+        <v>84</v>
+      </c>
+      <c r="G50" t="n">
+        <v>75.05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ben Griffin</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>53</v>
+      </c>
+      <c r="C51" t="n">
+        <v>65</v>
+      </c>
+      <c r="D51" t="n">
+        <v>72</v>
+      </c>
+      <c r="E51" t="n">
+        <v>78</v>
+      </c>
+      <c r="F51" t="n">
+        <v>82</v>
+      </c>
+      <c r="G51" t="n">
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Austin Eckroat</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="n">
+        <v>66</v>
+      </c>
+      <c r="D52" t="n">
+        <v>74</v>
+      </c>
+      <c r="E52" t="n">
+        <v>77</v>
+      </c>
+      <c r="F52" t="n">
+        <v>80</v>
+      </c>
+      <c r="G52" t="n">
+        <v>74.65000000000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Christiaan Bezuidenhout</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>60</v>
+      </c>
+      <c r="C53" t="n">
+        <v>61</v>
+      </c>
+      <c r="D53" t="n">
+        <v>68</v>
+      </c>
+      <c r="E53" t="n">
+        <v>80</v>
+      </c>
+      <c r="F53" t="n">
+        <v>86</v>
+      </c>
+      <c r="G53" t="n">
+        <v>74.40000000000001</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Keith Mitchell</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" t="n">
+        <v>68</v>
+      </c>
+      <c r="D54" t="n">
+        <v>83</v>
+      </c>
+      <c r="E54" t="n">
+        <v>72</v>
+      </c>
+      <c r="F54" t="n">
+        <v>74</v>
+      </c>
+      <c r="G54" t="n">
+        <v>74.34999999999999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Davis Thompson</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>50</v>
+      </c>
+      <c r="C55" t="n">
+        <v>66</v>
+      </c>
+      <c r="D55" t="n">
+        <v>76</v>
+      </c>
+      <c r="E55" t="n">
+        <v>75</v>
+      </c>
+      <c r="F55" t="n">
+        <v>79</v>
+      </c>
+      <c r="G55" t="n">
+        <v>74.25</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Emiliano Grillo</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>56</v>
+      </c>
+      <c r="C56" t="n">
+        <v>63</v>
+      </c>
+      <c r="D56" t="n">
+        <v>72</v>
+      </c>
+      <c r="E56" t="n">
+        <v>79</v>
+      </c>
+      <c r="F56" t="n">
+        <v>80</v>
+      </c>
+      <c r="G56" t="n">
+        <v>74.25</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Brendon Todd</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>57</v>
+      </c>
+      <c r="C57" t="n">
+        <v>63</v>
+      </c>
+      <c r="D57" t="n">
+        <v>65</v>
+      </c>
+      <c r="E57" t="n">
+        <v>78</v>
+      </c>
+      <c r="F57" t="n">
+        <v>90</v>
+      </c>
+      <c r="G57" t="n">
+        <v>74.15000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Billy Horschel</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>59</v>
+      </c>
+      <c r="C58" t="n">
+        <v>62</v>
+      </c>
+      <c r="D58" t="n">
+        <v>71</v>
+      </c>
+      <c r="E58" t="n">
+        <v>77</v>
+      </c>
+      <c r="F58" t="n">
+        <v>84</v>
+      </c>
+      <c r="G58" t="n">
+        <v>73.90000000000001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Taylor Pendrith</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>54</v>
+      </c>
+      <c r="C59" t="n">
+        <v>64</v>
+      </c>
+      <c r="D59" t="n">
+        <v>82</v>
+      </c>
+      <c r="E59" t="n">
+        <v>71</v>
+      </c>
+      <c r="F59" t="n">
+        <v>74</v>
+      </c>
+      <c r="G59" t="n">
+        <v>72.94999999999999</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jake Knapp</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>52</v>
+      </c>
+      <c r="C60" t="n">
+        <v>65</v>
+      </c>
+      <c r="D60" t="n">
+        <v>81</v>
+      </c>
+      <c r="E60" t="n">
+        <v>70</v>
+      </c>
+      <c r="F60" t="n">
+        <v>75</v>
+      </c>
+      <c r="G60" t="n">
+        <v>72.75</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gary Woodland</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" t="n">
+        <v>62</v>
+      </c>
+      <c r="D61" t="n">
+        <v>78</v>
+      </c>
+      <c r="E61" t="n">
+        <v>70</v>
+      </c>
+      <c r="F61" t="n">
+        <v>77</v>
+      </c>
+      <c r="G61" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>High Temp</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Low Temp</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rain Chance %</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Max Wind MPH</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>56</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>47</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>72</v>
+      </c>
+      <c r="D5" t="n">
+        <v>58</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>67</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>61</v>
+      </c>
+      <c r="D7" t="n">
+        <v>47</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>World Rank</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Base Rating</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Driving Rating</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Iron Rating</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Putting Rating</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Course Fit Score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Weather Difficulty Adjustment</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Final Projection Score</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Projected Rank</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Prediction Tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Scottie Scheffler</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" t="n">
+        <v>94</v>
+      </c>
+      <c r="G2" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>95.5925</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rory McIlroy</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>91</v>
+      </c>
+      <c r="G3" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>93.765</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Xander Schauffele</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D4" t="n">
+        <v>94</v>
+      </c>
+      <c r="E4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G4" t="n">
+        <v>92.69999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>92.765</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Collin Morikawa</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>93</v>
+      </c>
+      <c r="D5" t="n">
+        <v>91</v>
+      </c>
+      <c r="E5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F5" t="n">
+        <v>88</v>
+      </c>
+      <c r="G5" t="n">
+        <v>92.54999999999998</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>91.7475</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ludvig Aberg</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>92</v>
+      </c>
+      <c r="D6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" t="n">
+        <v>87</v>
+      </c>
+      <c r="G6" t="n">
+        <v>90.80000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>90.41000000000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Viktor Hovland</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>91</v>
+      </c>
+      <c r="D7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" t="n">
+        <v>88</v>
+      </c>
+      <c r="F7" t="n">
+        <v>86</v>
+      </c>
+      <c r="G7" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>88.91499999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Patrick Cantlay</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>88</v>
+      </c>
+      <c r="E8" t="n">
+        <v>91</v>
+      </c>
+      <c r="F8" t="n">
+        <v>89</v>
+      </c>
+      <c r="G8" t="n">
+        <v>89.64999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>88.7925</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wyndham Clark</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D9" t="n">
+        <v>92</v>
+      </c>
+      <c r="E9" t="n">
+        <v>84</v>
+      </c>
+      <c r="F9" t="n">
+        <v>86</v>
+      </c>
+      <c r="G9" t="n">
+        <v>87.39999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hideki Matsuyama</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>88</v>
+      </c>
+      <c r="D10" t="n">
+        <v>87</v>
+      </c>
+      <c r="E10" t="n">
+        <v>90</v>
+      </c>
+      <c r="F10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G10" t="n">
+        <v>87.84999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>86.88250000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tommy Fleetwood</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>88</v>
+      </c>
+      <c r="D11" t="n">
+        <v>86</v>
+      </c>
+      <c r="E11" t="n">
+        <v>91</v>
+      </c>
+      <c r="F11" t="n">
+        <v>84</v>
+      </c>
+      <c r="G11" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>86.6875</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Top Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Max Homa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>87</v>
+      </c>
+      <c r="D12" t="n">
+        <v>85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>86</v>
+      </c>
+      <c r="G12" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>85.64250000000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Justin Thomas</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>86</v>
+      </c>
+      <c r="D13" t="n">
+        <v>87</v>
+      </c>
+      <c r="E13" t="n">
+        <v>84</v>
+      </c>
+      <c r="F13" t="n">
+        <v>83</v>
+      </c>
+      <c r="G13" t="n">
+        <v>84.95</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>84.3275</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jordan Spieth</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E14" t="n">
+        <v>82</v>
+      </c>
+      <c r="F14" t="n">
+        <v>90</v>
+      </c>
+      <c r="G14" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>83.55249999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tony Finau</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" t="n">
+        <v>84</v>
+      </c>
+      <c r="D15" t="n">
+        <v>88</v>
+      </c>
+      <c r="E15" t="n">
+        <v>82</v>
+      </c>
+      <c r="F15" t="n">
+        <v>81</v>
+      </c>
+      <c r="G15" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>82.515</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sam Burns</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="n">
+        <v>84</v>
+      </c>
+      <c r="D16" t="n">
+        <v>86</v>
+      </c>
+      <c r="E16" t="n">
+        <v>80</v>
+      </c>
+      <c r="F16" t="n">
+        <v>85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>82.48500000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sahith Theegala</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>17</v>
+      </c>
+      <c r="C17" t="n">
+        <v>83</v>
+      </c>
+      <c r="D17" t="n">
+        <v>84</v>
+      </c>
+      <c r="E17" t="n">
+        <v>80</v>
+      </c>
+      <c r="F17" t="n">
+        <v>86</v>
+      </c>
+      <c r="G17" t="n">
+        <v>82.80000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>81.41000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cameron Young</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>83</v>
+      </c>
+      <c r="D18" t="n">
+        <v>90</v>
+      </c>
+      <c r="E18" t="n">
+        <v>78</v>
+      </c>
+      <c r="F18" t="n">
+        <v>79</v>
+      </c>
+      <c r="G18" t="n">
+        <v>82.19999999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>81.28999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Russell Henley</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="n">
+        <v>82</v>
+      </c>
+      <c r="D19" t="n">
+        <v>78</v>
+      </c>
+      <c r="E19" t="n">
+        <v>88</v>
+      </c>
+      <c r="F19" t="n">
+        <v>83</v>
+      </c>
+      <c r="G19" t="n">
+        <v>83.30000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>81.08500000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Matt Fitzpatrick</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="n">
+        <v>82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>79</v>
+      </c>
+      <c r="E20" t="n">
+        <v>86</v>
+      </c>
+      <c r="F20" t="n">
+        <v>84</v>
+      </c>
+      <c r="G20" t="n">
+        <v>83.05</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>80.82250000000002</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Keegan Bradley</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="n">
+        <v>81</v>
+      </c>
+      <c r="D21" t="n">
+        <v>82</v>
+      </c>
+      <c r="E21" t="n">
+        <v>84</v>
+      </c>
+      <c r="F21" t="n">
+        <v>80</v>
+      </c>
+      <c r="G21" t="n">
+        <v>82.10000000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>79.845</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brian Harman</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="n">
+        <v>81</v>
+      </c>
+      <c r="D22" t="n">
+        <v>76</v>
+      </c>
+      <c r="E22" t="n">
+        <v>87</v>
+      </c>
+      <c r="F22" t="n">
+        <v>83</v>
+      </c>
+      <c r="G22" t="n">
+        <v>82.25000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>79.7625</v>
+      </c>
+      <c r="J22" t="n">
+        <v>21</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jason Day</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>80</v>
+      </c>
+      <c r="D23" t="n">
+        <v>78</v>
+      </c>
+      <c r="E23" t="n">
+        <v>82</v>
+      </c>
+      <c r="F23" t="n">
+        <v>86</v>
+      </c>
+      <c r="G23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>78.83</v>
+      </c>
+      <c r="J23" t="n">
+        <v>22</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sepp Straka</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>80</v>
+      </c>
+      <c r="D24" t="n">
+        <v>81</v>
+      </c>
+      <c r="E24" t="n">
+        <v>83</v>
+      </c>
+      <c r="F24" t="n">
+        <v>79</v>
+      </c>
+      <c r="G24" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>78.545</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Min Woo Lee</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="n">
+        <v>79</v>
+      </c>
+      <c r="D25" t="n">
+        <v>86</v>
+      </c>
+      <c r="E25" t="n">
+        <v>77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>81</v>
+      </c>
+      <c r="G25" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>77.70250000000001</v>
+      </c>
+      <c r="J25" t="n">
+        <v>24</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Akshay Bhatia</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>79</v>
+      </c>
+      <c r="D26" t="n">
+        <v>80</v>
+      </c>
+      <c r="E26" t="n">
+        <v>82</v>
+      </c>
+      <c r="F26" t="n">
+        <v>80</v>
+      </c>
+      <c r="G26" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>77.575</v>
+      </c>
+      <c r="J26" t="n">
+        <v>25</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Strong Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Corey Conners</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="n">
+        <v>78</v>
+      </c>
+      <c r="D27" t="n">
+        <v>79</v>
+      </c>
+      <c r="E27" t="n">
+        <v>86</v>
+      </c>
+      <c r="F27" t="n">
+        <v>76</v>
+      </c>
+      <c r="G27" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>77.0925</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Adam Scott</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="n">
+        <v>78</v>
+      </c>
+      <c r="D28" t="n">
+        <v>81</v>
+      </c>
+      <c r="E28" t="n">
+        <v>80</v>
+      </c>
+      <c r="F28" t="n">
+        <v>82</v>
+      </c>
+      <c r="G28" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>76.7625</v>
+      </c>
+      <c r="J28" t="n">
+        <v>27</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shane Lowry</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>29</v>
+      </c>
+      <c r="C29" t="n">
+        <v>77</v>
+      </c>
+      <c r="D29" t="n">
+        <v>75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>84</v>
+      </c>
+      <c r="F29" t="n">
+        <v>86</v>
+      </c>
+      <c r="G29" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>76.28750000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>28</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Si Woo Kim</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>77</v>
+      </c>
+      <c r="D30" t="n">
+        <v>79</v>
+      </c>
+      <c r="E30" t="n">
+        <v>81</v>
+      </c>
+      <c r="F30" t="n">
+        <v>80</v>
+      </c>
+      <c r="G30" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="J30" t="n">
+        <v>29</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Rickie Fowler</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>76</v>
+      </c>
+      <c r="D31" t="n">
+        <v>78</v>
+      </c>
+      <c r="E31" t="n">
+        <v>80</v>
+      </c>
+      <c r="F31" t="n">
+        <v>82</v>
+      </c>
+      <c r="G31" t="n">
+        <v>79.10000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>74.995</v>
+      </c>
+      <c r="J31" t="n">
+        <v>30</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Will Zalatoris</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="n">
+        <v>76</v>
+      </c>
+      <c r="D32" t="n">
+        <v>83</v>
+      </c>
+      <c r="E32" t="n">
+        <v>79</v>
+      </c>
+      <c r="F32" t="n">
+        <v>74</v>
+      </c>
+      <c r="G32" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>74.53</v>
+      </c>
+      <c r="J32" t="n">
+        <v>31</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Denny McCarthy</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="n">
+        <v>75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>72</v>
+      </c>
+      <c r="E33" t="n">
+        <v>78</v>
+      </c>
+      <c r="F33" t="n">
+        <v>92</v>
+      </c>
+      <c r="G33" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>74.11499999999999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>32</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tom Kim</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="n">
+        <v>75</v>
+      </c>
+      <c r="D34" t="n">
+        <v>74</v>
+      </c>
+      <c r="E34" t="n">
+        <v>83</v>
+      </c>
+      <c r="F34" t="n">
+        <v>81</v>
+      </c>
+      <c r="G34" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>73.9875</v>
+      </c>
+      <c r="J34" t="n">
+        <v>33</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>J.T. Poston</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C35" t="n">
+        <v>74</v>
+      </c>
+      <c r="D35" t="n">
+        <v>72</v>
+      </c>
+      <c r="E35" t="n">
+        <v>81</v>
+      </c>
+      <c r="F35" t="n">
+        <v>86</v>
+      </c>
+      <c r="G35" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>73.1075</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Eric Cole</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="n">
+        <v>74</v>
+      </c>
+      <c r="D36" t="n">
+        <v>73</v>
+      </c>
+      <c r="E36" t="n">
+        <v>79</v>
+      </c>
+      <c r="F36" t="n">
+        <v>84</v>
+      </c>
+      <c r="G36" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="J36" t="n">
+        <v>35</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chris Kirk</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="n">
+        <v>73</v>
+      </c>
+      <c r="D37" t="n">
+        <v>74</v>
+      </c>
+      <c r="E37" t="n">
+        <v>80</v>
+      </c>
+      <c r="F37" t="n">
+        <v>82</v>
+      </c>
+      <c r="G37" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>72.175</v>
+      </c>
+      <c r="J37" t="n">
+        <v>36</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Byeong Hun An</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="n">
+        <v>73</v>
+      </c>
+      <c r="D38" t="n">
+        <v>82</v>
+      </c>
+      <c r="E38" t="n">
+        <v>75</v>
+      </c>
+      <c r="F38" t="n">
+        <v>76</v>
+      </c>
+      <c r="G38" t="n">
+        <v>76.55000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>71.59750000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>37</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Harris English</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="n">
+        <v>72</v>
+      </c>
+      <c r="D39" t="n">
+        <v>75</v>
+      </c>
+      <c r="E39" t="n">
+        <v>79</v>
+      </c>
+      <c r="F39" t="n">
+        <v>81</v>
+      </c>
+      <c r="G39" t="n">
+        <v>77</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="J39" t="n">
+        <v>38</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lucas Glover</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="n">
+        <v>72</v>
+      </c>
+      <c r="D40" t="n">
+        <v>76</v>
+      </c>
+      <c r="E40" t="n">
+        <v>82</v>
+      </c>
+      <c r="F40" t="n">
+        <v>75</v>
+      </c>
+      <c r="G40" t="n">
+        <v>77.10000000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>71.14500000000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>39</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Maverick McNealy</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="n">
+        <v>71</v>
+      </c>
+      <c r="D41" t="n">
+        <v>73</v>
+      </c>
+      <c r="E41" t="n">
+        <v>78</v>
+      </c>
+      <c r="F41" t="n">
+        <v>84</v>
+      </c>
+      <c r="G41" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>70.3475</v>
+      </c>
+      <c r="J41" t="n">
+        <v>40</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Taylor Moore</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="n">
+        <v>71</v>
+      </c>
+      <c r="D42" t="n">
+        <v>75</v>
+      </c>
+      <c r="E42" t="n">
+        <v>76</v>
+      </c>
+      <c r="F42" t="n">
+        <v>82</v>
+      </c>
+      <c r="G42" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>69.92749999999999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>41</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kurt Kitayama</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="n">
+        <v>70</v>
+      </c>
+      <c r="D43" t="n">
+        <v>79</v>
+      </c>
+      <c r="E43" t="n">
+        <v>74</v>
+      </c>
+      <c r="F43" t="n">
+        <v>78</v>
+      </c>
+      <c r="G43" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>69.0625</v>
+      </c>
+      <c r="J43" t="n">
+        <v>42</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Nicolai Hojgaard</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="n">
+        <v>70</v>
+      </c>
+      <c r="D44" t="n">
+        <v>82</v>
+      </c>
+      <c r="E44" t="n">
+        <v>73</v>
+      </c>
+      <c r="F44" t="n">
+        <v>76</v>
+      </c>
+      <c r="G44" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>68.91250000000001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>43</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Adam Hadwin</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>45</v>
+      </c>
+      <c r="C45" t="n">
+        <v>69</v>
+      </c>
+      <c r="D45" t="n">
+        <v>72</v>
+      </c>
+      <c r="E45" t="n">
+        <v>80</v>
+      </c>
+      <c r="F45" t="n">
+        <v>82</v>
+      </c>
+      <c r="G45" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>68.64</v>
+      </c>
+      <c r="J45" t="n">
+        <v>44</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Cam Davis</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" t="n">
+        <v>69</v>
+      </c>
+      <c r="D46" t="n">
+        <v>78</v>
+      </c>
+      <c r="E46" t="n">
+        <v>74</v>
+      </c>
+      <c r="F46" t="n">
+        <v>80</v>
+      </c>
+      <c r="G46" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="J46" t="n">
+        <v>45</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Nick Taylor</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="n">
+        <v>68</v>
+      </c>
+      <c r="D47" t="n">
+        <v>71</v>
+      </c>
+      <c r="E47" t="n">
+        <v>79</v>
+      </c>
+      <c r="F47" t="n">
+        <v>83</v>
+      </c>
+      <c r="G47" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="J47" t="n">
+        <v>46</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Andrew Putnam</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>49</v>
+      </c>
+      <c r="C48" t="n">
+        <v>67</v>
+      </c>
+      <c r="D48" t="n">
+        <v>68</v>
+      </c>
+      <c r="E48" t="n">
+        <v>81</v>
+      </c>
+      <c r="F48" t="n">
+        <v>86</v>
+      </c>
+      <c r="G48" t="n">
+        <v>75.95</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I48" t="n">
+        <v>67.12750000000001</v>
+      </c>
+      <c r="J48" t="n">
+        <v>47</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Keith Mitchell</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" t="n">
+        <v>68</v>
+      </c>
+      <c r="D49" t="n">
+        <v>83</v>
+      </c>
+      <c r="E49" t="n">
+        <v>72</v>
+      </c>
+      <c r="F49" t="n">
+        <v>74</v>
+      </c>
+      <c r="G49" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>67.1075</v>
+      </c>
+      <c r="J49" t="n">
+        <v>48</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Beau Hossler</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" t="n">
+        <v>67</v>
+      </c>
+      <c r="D50" t="n">
+        <v>73</v>
+      </c>
+      <c r="E50" t="n">
+        <v>76</v>
+      </c>
+      <c r="F50" t="n">
+        <v>84</v>
+      </c>
+      <c r="G50" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I50" t="n">
+        <v>66.8725</v>
+      </c>
+      <c r="J50" t="n">
+        <v>49</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Austin Eckroat</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>51</v>
+      </c>
+      <c r="C51" t="n">
+        <v>66</v>
+      </c>
+      <c r="D51" t="n">
+        <v>74</v>
+      </c>
+      <c r="E51" t="n">
+        <v>77</v>
+      </c>
+      <c r="F51" t="n">
+        <v>80</v>
+      </c>
+      <c r="G51" t="n">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>65.8425</v>
+      </c>
+      <c r="J51" t="n">
+        <v>50</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Davis Thompson</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" t="n">
+        <v>66</v>
+      </c>
+      <c r="D52" t="n">
+        <v>76</v>
+      </c>
+      <c r="E52" t="n">
+        <v>75</v>
+      </c>
+      <c r="F52" t="n">
+        <v>79</v>
+      </c>
+      <c r="G52" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>65.8125</v>
+      </c>
+      <c r="J52" t="n">
+        <v>51</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ben Griffin</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>53</v>
+      </c>
+      <c r="C53" t="n">
+        <v>65</v>
+      </c>
+      <c r="D53" t="n">
+        <v>72</v>
+      </c>
+      <c r="E53" t="n">
+        <v>78</v>
+      </c>
+      <c r="F53" t="n">
+        <v>82</v>
+      </c>
+      <c r="G53" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>65.16500000000001</v>
+      </c>
+      <c r="J53" t="n">
+        <v>52</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Alex Noren</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>55</v>
+      </c>
+      <c r="C54" t="n">
+        <v>64</v>
+      </c>
+      <c r="D54" t="n">
+        <v>70</v>
+      </c>
+      <c r="E54" t="n">
+        <v>82</v>
+      </c>
+      <c r="F54" t="n">
+        <v>83</v>
+      </c>
+      <c r="G54" t="n">
+        <v>75.60000000000001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="J54" t="n">
+        <v>53</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jake Knapp</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="n">
+        <v>65</v>
+      </c>
+      <c r="D55" t="n">
+        <v>81</v>
+      </c>
+      <c r="E55" t="n">
+        <v>70</v>
+      </c>
+      <c r="F55" t="n">
+        <v>75</v>
+      </c>
+      <c r="G55" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>64.4375</v>
+      </c>
+      <c r="J55" t="n">
+        <v>54</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Taylor Pendrith</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" t="n">
+        <v>64</v>
+      </c>
+      <c r="D56" t="n">
+        <v>82</v>
+      </c>
+      <c r="E56" t="n">
+        <v>71</v>
+      </c>
+      <c r="F56" t="n">
+        <v>74</v>
+      </c>
+      <c r="G56" t="n">
+        <v>72.94999999999999</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>63.8275</v>
+      </c>
+      <c r="J56" t="n">
+        <v>55</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Emiliano Grillo</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="n">
+        <v>63</v>
+      </c>
+      <c r="D57" t="n">
+        <v>72</v>
+      </c>
+      <c r="E57" t="n">
+        <v>79</v>
+      </c>
+      <c r="F57" t="n">
+        <v>80</v>
+      </c>
+      <c r="G57" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>63.71250000000001</v>
+      </c>
+      <c r="J57" t="n">
+        <v>56</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Brendon Todd</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="n">
+        <v>63</v>
+      </c>
+      <c r="D58" t="n">
+        <v>65</v>
+      </c>
+      <c r="E58" t="n">
+        <v>78</v>
+      </c>
+      <c r="F58" t="n">
+        <v>90</v>
+      </c>
+      <c r="G58" t="n">
+        <v>74.15000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>63.51750000000001</v>
+      </c>
+      <c r="J58" t="n">
+        <v>57</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Billy Horschel</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>59</v>
+      </c>
+      <c r="C59" t="n">
+        <v>62</v>
+      </c>
+      <c r="D59" t="n">
+        <v>71</v>
+      </c>
+      <c r="E59" t="n">
+        <v>77</v>
+      </c>
+      <c r="F59" t="n">
+        <v>84</v>
+      </c>
+      <c r="G59" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I59" t="n">
+        <v>62.70500000000001</v>
+      </c>
+      <c r="J59" t="n">
+        <v>58</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Christiaan Bezuidenhout</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>60</v>
+      </c>
+      <c r="C60" t="n">
+        <v>61</v>
+      </c>
+      <c r="D60" t="n">
+        <v>68</v>
+      </c>
+      <c r="E60" t="n">
+        <v>80</v>
+      </c>
+      <c r="F60" t="n">
+        <v>86</v>
+      </c>
+      <c r="G60" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>62.38000000000001</v>
+      </c>
+      <c r="J60" t="n">
+        <v>59</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gary Woodland</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" t="n">
+        <v>62</v>
+      </c>
+      <c r="D61" t="n">
+        <v>78</v>
+      </c>
+      <c r="E61" t="n">
+        <v>70</v>
+      </c>
+      <c r="F61" t="n">
+        <v>77</v>
+      </c>
+      <c r="G61" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I61" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="J61" t="n">
+        <v>60</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Open-Meteo Weather</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Free weather forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Manual Player Ratings</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Starter golfer ratings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Manual Course Fit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Current Course</t>
+          <t>Course-style weighting</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GitHub Actions</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Weekly spreadsheet update</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Edit player list in main.py when needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Edit course latitude/longitude in main.py for each tournament.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GitHub Actions runs weekly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Download golf_model.xlsx after workflow finishes.</t>
         </is>
       </c>
     </row>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-26 22:43</t>
+          <t>2026-06-01 17:13</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49.7</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>71.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83.8</v>
+        <v>80</v>
       </c>
       <c r="C3" t="n">
-        <v>72</v>
+        <v>67.7</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>8.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89.5</v>
+        <v>80.3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.3</v>
+        <v>57.8</v>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>86.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="C5" t="n">
-        <v>72</v>
+        <v>62.7</v>
       </c>
       <c r="D5" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.5</v>
+        <v>89.8</v>
       </c>
       <c r="C6" t="n">
-        <v>69.3</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>11.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78.7</v>
+        <v>89.2</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>68.8</v>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>62.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -3820,10 +3820,10 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>95.5925</v>
+        <v>97.0925</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -3859,10 +3859,10 @@
         <v>93.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>93.765</v>
+        <v>95.265</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -3898,10 +3898,10 @@
         <v>92.69999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>92.765</v>
+        <v>94.265</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -3937,10 +3937,10 @@
         <v>92.54999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>91.7475</v>
+        <v>93.2475</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -3976,10 +3976,10 @@
         <v>90.80000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>90.41000000000001</v>
+        <v>91.91000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -4015,10 +4015,10 @@
         <v>88.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>88.91499999999999</v>
+        <v>90.41499999999999</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
@@ -4054,10 +4054,10 @@
         <v>89.64999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>88.7925</v>
+        <v>90.2925</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
@@ -4093,10 +4093,10 @@
         <v>87.39999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>87.23</v>
+        <v>88.73</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
@@ -4132,10 +4132,10 @@
         <v>87.84999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>86.88250000000001</v>
+        <v>88.38250000000001</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -4171,10 +4171,10 @@
         <v>87.75</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>86.6875</v>
+        <v>88.1875</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
@@ -4210,10 +4210,10 @@
         <v>86.65000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>85.64250000000001</v>
+        <v>87.14250000000001</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
@@ -4249,10 +4249,10 @@
         <v>84.95</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>84.3275</v>
+        <v>85.8275</v>
       </c>
       <c r="J13" t="n">
         <v>12</v>
@@ -4288,10 +4288,10 @@
         <v>84.45</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>83.55249999999999</v>
+        <v>85.05249999999999</v>
       </c>
       <c r="J14" t="n">
         <v>13</v>
@@ -4327,10 +4327,10 @@
         <v>83.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>82.515</v>
+        <v>84.015</v>
       </c>
       <c r="J15" t="n">
         <v>14</v>
@@ -4366,10 +4366,10 @@
         <v>83.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>82.48500000000001</v>
+        <v>83.98500000000001</v>
       </c>
       <c r="J16" t="n">
         <v>15</v>
@@ -4405,10 +4405,10 @@
         <v>82.80000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>81.41000000000001</v>
+        <v>82.91000000000001</v>
       </c>
       <c r="J17" t="n">
         <v>16</v>
@@ -4444,10 +4444,10 @@
         <v>82.19999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>81.28999999999999</v>
+        <v>82.78999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>17</v>
@@ -4483,10 +4483,10 @@
         <v>83.30000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>81.08500000000001</v>
+        <v>82.58500000000001</v>
       </c>
       <c r="J19" t="n">
         <v>18</v>
@@ -4522,10 +4522,10 @@
         <v>83.05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>80.82250000000002</v>
+        <v>82.32250000000002</v>
       </c>
       <c r="J20" t="n">
         <v>19</v>
@@ -4561,10 +4561,10 @@
         <v>82.10000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>79.845</v>
+        <v>81.345</v>
       </c>
       <c r="J21" t="n">
         <v>20</v>
@@ -4600,10 +4600,10 @@
         <v>82.25000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>79.7625</v>
+        <v>81.2625</v>
       </c>
       <c r="J22" t="n">
         <v>21</v>
@@ -4639,10 +4639,10 @@
         <v>81.40000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>78.83</v>
+        <v>80.33</v>
       </c>
       <c r="J23" t="n">
         <v>22</v>
@@ -4678,10 +4678,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>78.545</v>
+        <v>80.045</v>
       </c>
       <c r="J24" t="n">
         <v>23</v>
@@ -4717,10 +4717,10 @@
         <v>80.45</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>77.70250000000001</v>
+        <v>79.20250000000001</v>
       </c>
       <c r="J25" t="n">
         <v>24</v>
@@ -4756,10 +4756,10 @@
         <v>80.5</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>77.575</v>
+        <v>79.075</v>
       </c>
       <c r="J26" t="n">
         <v>25</v>
@@ -4795,10 +4795,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>77.0925</v>
+        <v>78.5925</v>
       </c>
       <c r="J27" t="n">
         <v>26</v>
@@ -4834,10 +4834,10 @@
         <v>80.25</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>76.7625</v>
+        <v>78.2625</v>
       </c>
       <c r="J28" t="n">
         <v>27</v>
@@ -4873,10 +4873,10 @@
         <v>80.75</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>76.28750000000001</v>
+        <v>77.78750000000001</v>
       </c>
       <c r="J29" t="n">
         <v>28</v>
@@ -4912,10 +4912,10 @@
         <v>79.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>75.875</v>
+        <v>77.375</v>
       </c>
       <c r="J30" t="n">
         <v>29</v>
@@ -4951,10 +4951,10 @@
         <v>79.10000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>74.995</v>
+        <v>76.495</v>
       </c>
       <c r="J31" t="n">
         <v>30</v>
@@ -4990,10 +4990,10 @@
         <v>78.40000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>74.53</v>
+        <v>76.03</v>
       </c>
       <c r="J32" t="n">
         <v>31</v>
@@ -5029,10 +5029,10 @@
         <v>78.7</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>74.11499999999999</v>
+        <v>75.61499999999999</v>
       </c>
       <c r="J33" t="n">
         <v>32</v>
@@ -5068,10 +5068,10 @@
         <v>78.75</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>73.9875</v>
+        <v>75.4875</v>
       </c>
       <c r="J34" t="n">
         <v>33</v>
@@ -5107,10 +5107,10 @@
         <v>78.34999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>73.1075</v>
+        <v>74.6075</v>
       </c>
       <c r="J35" t="n">
         <v>34</v>
@@ -5146,10 +5146,10 @@
         <v>77.5</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>72.875</v>
+        <v>74.375</v>
       </c>
       <c r="J36" t="n">
         <v>35</v>
@@ -5185,10 +5185,10 @@
         <v>77.5</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>72.175</v>
+        <v>73.675</v>
       </c>
       <c r="J37" t="n">
         <v>36</v>
@@ -5224,10 +5224,10 @@
         <v>76.55000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>71.59750000000001</v>
+        <v>73.09750000000001</v>
       </c>
       <c r="J38" t="n">
         <v>37</v>
@@ -5263,10 +5263,10 @@
         <v>77</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>71.25</v>
+        <v>72.75</v>
       </c>
       <c r="J39" t="n">
         <v>38</v>
@@ -5302,10 +5302,10 @@
         <v>77.10000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>71.14500000000001</v>
+        <v>72.64500000000001</v>
       </c>
       <c r="J40" t="n">
         <v>39</v>
@@ -5341,10 +5341,10 @@
         <v>76.55</v>
       </c>
       <c r="H41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>70.3475</v>
+        <v>71.8475</v>
       </c>
       <c r="J41" t="n">
         <v>40</v>
@@ -5380,10 +5380,10 @@
         <v>75.95</v>
       </c>
       <c r="H42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>69.92749999999999</v>
+        <v>71.42749999999999</v>
       </c>
       <c r="J42" t="n">
         <v>41</v>
@@ -5419,10 +5419,10 @@
         <v>75.25</v>
       </c>
       <c r="H43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>69.0625</v>
+        <v>70.5625</v>
       </c>
       <c r="J43" t="n">
         <v>42</v>
@@ -5458,10 +5458,10 @@
         <v>75.25</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>68.91250000000001</v>
+        <v>70.41250000000001</v>
       </c>
       <c r="J44" t="n">
         <v>43</v>
@@ -5497,10 +5497,10 @@
         <v>76.2</v>
       </c>
       <c r="H45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>68.64</v>
+        <v>70.14</v>
       </c>
       <c r="J45" t="n">
         <v>44</v>
@@ -5536,10 +5536,10 @@
         <v>75.2</v>
       </c>
       <c r="H46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>68.34</v>
+        <v>69.84</v>
       </c>
       <c r="J46" t="n">
         <v>45</v>
@@ -5575,10 +5575,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>67.81999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>46</v>
@@ -5614,10 +5614,10 @@
         <v>75.95</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>67.12750000000001</v>
+        <v>68.62750000000001</v>
       </c>
       <c r="J48" t="n">
         <v>47</v>
@@ -5653,10 +5653,10 @@
         <v>74.34999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>67.1075</v>
+        <v>68.6075</v>
       </c>
       <c r="J49" t="n">
         <v>48</v>
@@ -5692,10 +5692,10 @@
         <v>75.05</v>
       </c>
       <c r="H50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>66.8725</v>
+        <v>68.3725</v>
       </c>
       <c r="J50" t="n">
         <v>49</v>
@@ -5731,10 +5731,10 @@
         <v>74.65000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>65.8425</v>
+        <v>67.3425</v>
       </c>
       <c r="J51" t="n">
         <v>50</v>
@@ -5770,10 +5770,10 @@
         <v>74.25</v>
       </c>
       <c r="H52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>65.8125</v>
+        <v>67.3125</v>
       </c>
       <c r="J52" t="n">
         <v>51</v>
@@ -5809,10 +5809,10 @@
         <v>74.7</v>
       </c>
       <c r="H53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>65.16500000000001</v>
+        <v>66.66500000000001</v>
       </c>
       <c r="J53" t="n">
         <v>52</v>
@@ -5848,10 +5848,10 @@
         <v>75.60000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>64.87</v>
+        <v>66.37</v>
       </c>
       <c r="J54" t="n">
         <v>53</v>
@@ -5887,10 +5887,10 @@
         <v>72.75</v>
       </c>
       <c r="H55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>64.4375</v>
+        <v>65.9375</v>
       </c>
       <c r="J55" t="n">
         <v>54</v>
@@ -5926,10 +5926,10 @@
         <v>72.94999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>63.8275</v>
+        <v>65.3275</v>
       </c>
       <c r="J56" t="n">
         <v>55</v>
@@ -5965,10 +5965,10 @@
         <v>74.25</v>
       </c>
       <c r="H57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>63.71250000000001</v>
+        <v>65.21250000000001</v>
       </c>
       <c r="J57" t="n">
         <v>56</v>
@@ -6004,10 +6004,10 @@
         <v>74.15000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>63.51750000000001</v>
+        <v>65.01750000000001</v>
       </c>
       <c r="J58" t="n">
         <v>57</v>
@@ -6043,10 +6043,10 @@
         <v>73.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>62.70500000000001</v>
+        <v>64.20500000000001</v>
       </c>
       <c r="J59" t="n">
         <v>58</v>
@@ -6082,10 +6082,10 @@
         <v>74.40000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>62.38000000000001</v>
+        <v>63.88000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>59</v>
@@ -6121,10 +6121,10 @@
         <v>71.8</v>
       </c>
       <c r="H61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>61.91</v>
+        <v>63.41</v>
       </c>
       <c r="J61" t="n">
         <v>60</v>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01 17:13</t>
+          <t>2026-06-08 15:24</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.7</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>66.3</v>
+        <v>73.7</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>83.2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.7</v>
+        <v>73.8</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80.3</v>
+        <v>91.8</v>
       </c>
       <c r="C4" t="n">
-        <v>57.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>87</v>
+        <v>96.7</v>
       </c>
       <c r="C5" t="n">
-        <v>62.7</v>
+        <v>73.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89.8</v>
+        <v>100.3</v>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>78.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>89.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>68.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E7" t="n">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>95.8</v>
       </c>
       <c r="C8" t="n">
-        <v>70.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:24</t>
+          <t>2026-06-15 16:52</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.800000000000001</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.7</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="C2" t="n">
-        <v>73.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83.2</v>
+        <v>81.3</v>
       </c>
       <c r="C3" t="n">
-        <v>73.8</v>
+        <v>70.2</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>91.8</v>
+        <v>88.2</v>
       </c>
       <c r="C4" t="n">
-        <v>69.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="E4" t="n">
-        <v>7.4</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="C5" t="n">
-        <v>73.8</v>
+        <v>74</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>8.199999999999999</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>78.5</v>
+        <v>71.7</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E6" t="n">
-        <v>11.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>74.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -3820,10 +3820,10 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>97.0925</v>
+        <v>95.5925</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -3859,10 +3859,10 @@
         <v>93.7</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>95.265</v>
+        <v>93.765</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -3898,10 +3898,10 @@
         <v>92.69999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>94.265</v>
+        <v>92.765</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -3937,10 +3937,10 @@
         <v>92.54999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="n">
-        <v>93.2475</v>
+        <v>91.7475</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -3976,10 +3976,10 @@
         <v>90.80000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>91.91000000000001</v>
+        <v>90.41000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -4015,10 +4015,10 @@
         <v>88.7</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>90.41499999999999</v>
+        <v>88.91499999999999</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
@@ -4054,10 +4054,10 @@
         <v>89.64999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>90.2925</v>
+        <v>88.7925</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
@@ -4093,10 +4093,10 @@
         <v>87.39999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="n">
-        <v>88.73</v>
+        <v>87.23</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
@@ -4132,10 +4132,10 @@
         <v>87.84999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="n">
-        <v>88.38250000000001</v>
+        <v>86.88250000000001</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -4171,10 +4171,10 @@
         <v>87.75</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I11" t="n">
-        <v>88.1875</v>
+        <v>86.6875</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
@@ -4210,10 +4210,10 @@
         <v>86.65000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I12" t="n">
-        <v>87.14250000000001</v>
+        <v>85.64250000000001</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
@@ -4249,10 +4249,10 @@
         <v>84.95</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I13" t="n">
-        <v>85.8275</v>
+        <v>84.3275</v>
       </c>
       <c r="J13" t="n">
         <v>12</v>
@@ -4288,10 +4288,10 @@
         <v>84.45</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I14" t="n">
-        <v>85.05249999999999</v>
+        <v>83.55249999999999</v>
       </c>
       <c r="J14" t="n">
         <v>13</v>
@@ -4327,10 +4327,10 @@
         <v>83.7</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I15" t="n">
-        <v>84.015</v>
+        <v>82.515</v>
       </c>
       <c r="J15" t="n">
         <v>14</v>
@@ -4366,10 +4366,10 @@
         <v>83.3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I16" t="n">
-        <v>83.98500000000001</v>
+        <v>82.48500000000001</v>
       </c>
       <c r="J16" t="n">
         <v>15</v>
@@ -4405,10 +4405,10 @@
         <v>82.80000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>82.91000000000001</v>
+        <v>81.41000000000001</v>
       </c>
       <c r="J17" t="n">
         <v>16</v>
@@ -4444,10 +4444,10 @@
         <v>82.19999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I18" t="n">
-        <v>82.78999999999999</v>
+        <v>81.28999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>17</v>
@@ -4483,10 +4483,10 @@
         <v>83.30000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I19" t="n">
-        <v>82.58500000000001</v>
+        <v>81.08500000000001</v>
       </c>
       <c r="J19" t="n">
         <v>18</v>
@@ -4522,10 +4522,10 @@
         <v>83.05</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I20" t="n">
-        <v>82.32250000000002</v>
+        <v>80.82250000000002</v>
       </c>
       <c r="J20" t="n">
         <v>19</v>
@@ -4561,10 +4561,10 @@
         <v>82.10000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I21" t="n">
-        <v>81.345</v>
+        <v>79.845</v>
       </c>
       <c r="J21" t="n">
         <v>20</v>
@@ -4600,10 +4600,10 @@
         <v>82.25000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I22" t="n">
-        <v>81.2625</v>
+        <v>79.7625</v>
       </c>
       <c r="J22" t="n">
         <v>21</v>
@@ -4639,10 +4639,10 @@
         <v>81.40000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I23" t="n">
-        <v>80.33</v>
+        <v>78.83</v>
       </c>
       <c r="J23" t="n">
         <v>22</v>
@@ -4678,10 +4678,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I24" t="n">
-        <v>80.045</v>
+        <v>78.545</v>
       </c>
       <c r="J24" t="n">
         <v>23</v>
@@ -4717,10 +4717,10 @@
         <v>80.45</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I25" t="n">
-        <v>79.20250000000001</v>
+        <v>77.70250000000001</v>
       </c>
       <c r="J25" t="n">
         <v>24</v>
@@ -4756,10 +4756,10 @@
         <v>80.5</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I26" t="n">
-        <v>79.075</v>
+        <v>77.575</v>
       </c>
       <c r="J26" t="n">
         <v>25</v>
@@ -4795,10 +4795,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>78.5925</v>
+        <v>77.0925</v>
       </c>
       <c r="J27" t="n">
         <v>26</v>
@@ -4834,10 +4834,10 @@
         <v>80.25</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>78.2625</v>
+        <v>76.7625</v>
       </c>
       <c r="J28" t="n">
         <v>27</v>
@@ -4873,10 +4873,10 @@
         <v>80.75</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I29" t="n">
-        <v>77.78750000000001</v>
+        <v>76.28750000000001</v>
       </c>
       <c r="J29" t="n">
         <v>28</v>
@@ -4912,10 +4912,10 @@
         <v>79.5</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I30" t="n">
-        <v>77.375</v>
+        <v>75.875</v>
       </c>
       <c r="J30" t="n">
         <v>29</v>
@@ -4951,10 +4951,10 @@
         <v>79.10000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I31" t="n">
-        <v>76.495</v>
+        <v>74.995</v>
       </c>
       <c r="J31" t="n">
         <v>30</v>
@@ -4990,10 +4990,10 @@
         <v>78.40000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I32" t="n">
-        <v>76.03</v>
+        <v>74.53</v>
       </c>
       <c r="J32" t="n">
         <v>31</v>
@@ -5029,10 +5029,10 @@
         <v>78.7</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I33" t="n">
-        <v>75.61499999999999</v>
+        <v>74.11499999999999</v>
       </c>
       <c r="J33" t="n">
         <v>32</v>
@@ -5068,10 +5068,10 @@
         <v>78.75</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I34" t="n">
-        <v>75.4875</v>
+        <v>73.9875</v>
       </c>
       <c r="J34" t="n">
         <v>33</v>
@@ -5107,10 +5107,10 @@
         <v>78.34999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I35" t="n">
-        <v>74.6075</v>
+        <v>73.1075</v>
       </c>
       <c r="J35" t="n">
         <v>34</v>
@@ -5146,10 +5146,10 @@
         <v>77.5</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I36" t="n">
-        <v>74.375</v>
+        <v>72.875</v>
       </c>
       <c r="J36" t="n">
         <v>35</v>
@@ -5185,10 +5185,10 @@
         <v>77.5</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I37" t="n">
-        <v>73.675</v>
+        <v>72.175</v>
       </c>
       <c r="J37" t="n">
         <v>36</v>
@@ -5224,10 +5224,10 @@
         <v>76.55000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I38" t="n">
-        <v>73.09750000000001</v>
+        <v>71.59750000000001</v>
       </c>
       <c r="J38" t="n">
         <v>37</v>
@@ -5263,10 +5263,10 @@
         <v>77</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I39" t="n">
-        <v>72.75</v>
+        <v>71.25</v>
       </c>
       <c r="J39" t="n">
         <v>38</v>
@@ -5302,10 +5302,10 @@
         <v>77.10000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I40" t="n">
-        <v>72.64500000000001</v>
+        <v>71.14500000000001</v>
       </c>
       <c r="J40" t="n">
         <v>39</v>
@@ -5341,10 +5341,10 @@
         <v>76.55</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I41" t="n">
-        <v>71.8475</v>
+        <v>70.3475</v>
       </c>
       <c r="J41" t="n">
         <v>40</v>
@@ -5380,10 +5380,10 @@
         <v>75.95</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I42" t="n">
-        <v>71.42749999999999</v>
+        <v>69.92749999999999</v>
       </c>
       <c r="J42" t="n">
         <v>41</v>
@@ -5419,10 +5419,10 @@
         <v>75.25</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I43" t="n">
-        <v>70.5625</v>
+        <v>69.0625</v>
       </c>
       <c r="J43" t="n">
         <v>42</v>
@@ -5458,10 +5458,10 @@
         <v>75.25</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I44" t="n">
-        <v>70.41250000000001</v>
+        <v>68.91250000000001</v>
       </c>
       <c r="J44" t="n">
         <v>43</v>
@@ -5497,10 +5497,10 @@
         <v>76.2</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I45" t="n">
-        <v>70.14</v>
+        <v>68.64</v>
       </c>
       <c r="J45" t="n">
         <v>44</v>
@@ -5536,10 +5536,10 @@
         <v>75.2</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I46" t="n">
-        <v>69.84</v>
+        <v>68.34</v>
       </c>
       <c r="J46" t="n">
         <v>45</v>
@@ -5575,10 +5575,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I47" t="n">
-        <v>69.31999999999999</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>46</v>
@@ -5614,10 +5614,10 @@
         <v>75.95</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I48" t="n">
-        <v>68.62750000000001</v>
+        <v>67.12750000000001</v>
       </c>
       <c r="J48" t="n">
         <v>47</v>
@@ -5653,10 +5653,10 @@
         <v>74.34999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I49" t="n">
-        <v>68.6075</v>
+        <v>67.1075</v>
       </c>
       <c r="J49" t="n">
         <v>48</v>
@@ -5692,10 +5692,10 @@
         <v>75.05</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I50" t="n">
-        <v>68.3725</v>
+        <v>66.8725</v>
       </c>
       <c r="J50" t="n">
         <v>49</v>
@@ -5731,10 +5731,10 @@
         <v>74.65000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I51" t="n">
-        <v>67.3425</v>
+        <v>65.8425</v>
       </c>
       <c r="J51" t="n">
         <v>50</v>
@@ -5770,10 +5770,10 @@
         <v>74.25</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I52" t="n">
-        <v>67.3125</v>
+        <v>65.8125</v>
       </c>
       <c r="J52" t="n">
         <v>51</v>
@@ -5809,10 +5809,10 @@
         <v>74.7</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I53" t="n">
-        <v>66.66500000000001</v>
+        <v>65.16500000000001</v>
       </c>
       <c r="J53" t="n">
         <v>52</v>
@@ -5848,10 +5848,10 @@
         <v>75.60000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I54" t="n">
-        <v>66.37</v>
+        <v>64.87</v>
       </c>
       <c r="J54" t="n">
         <v>53</v>
@@ -5887,10 +5887,10 @@
         <v>72.75</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I55" t="n">
-        <v>65.9375</v>
+        <v>64.4375</v>
       </c>
       <c r="J55" t="n">
         <v>54</v>
@@ -5926,10 +5926,10 @@
         <v>72.94999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I56" t="n">
-        <v>65.3275</v>
+        <v>63.8275</v>
       </c>
       <c r="J56" t="n">
         <v>55</v>
@@ -5965,10 +5965,10 @@
         <v>74.25</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I57" t="n">
-        <v>65.21250000000001</v>
+        <v>63.71250000000001</v>
       </c>
       <c r="J57" t="n">
         <v>56</v>
@@ -6004,10 +6004,10 @@
         <v>74.15000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I58" t="n">
-        <v>65.01750000000001</v>
+        <v>63.51750000000001</v>
       </c>
       <c r="J58" t="n">
         <v>57</v>
@@ -6043,10 +6043,10 @@
         <v>73.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I59" t="n">
-        <v>64.20500000000001</v>
+        <v>62.70500000000001</v>
       </c>
       <c r="J59" t="n">
         <v>58</v>
@@ -6082,10 +6082,10 @@
         <v>74.40000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I60" t="n">
-        <v>63.88000000000001</v>
+        <v>62.38000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>59</v>
@@ -6121,10 +6121,10 @@
         <v>71.8</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I61" t="n">
-        <v>63.41</v>
+        <v>61.91</v>
       </c>
       <c r="J61" t="n">
         <v>60</v>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 16:52</t>
+          <t>2026-06-22 16:24</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45.7</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="10">
@@ -3594,74 +3594,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>72.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>70.2</v>
+        <v>74.7</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>70.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>14.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="C5" t="n">
-        <v>74</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>12.6</v>
@@ -3670,58 +3670,58 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77.09999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="C6" t="n">
-        <v>71.7</v>
+        <v>76.3</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>99.8</v>
       </c>
       <c r="C7" t="n">
-        <v>71.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>92.90000000000001</v>
+        <v>101.8</v>
       </c>
       <c r="C8" t="n">
-        <v>72</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3820,10 +3820,10 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>95.5925</v>
+        <v>97.0925</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -3859,10 +3859,10 @@
         <v>93.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>93.765</v>
+        <v>95.265</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -3898,10 +3898,10 @@
         <v>92.69999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>92.765</v>
+        <v>94.265</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -3937,10 +3937,10 @@
         <v>92.54999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>91.7475</v>
+        <v>93.2475</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
@@ -3976,10 +3976,10 @@
         <v>90.80000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>90.41000000000001</v>
+        <v>91.91000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -4015,10 +4015,10 @@
         <v>88.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>88.91499999999999</v>
+        <v>90.41499999999999</v>
       </c>
       <c r="J7" t="n">
         <v>6</v>
@@ -4054,10 +4054,10 @@
         <v>89.64999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>88.7925</v>
+        <v>90.2925</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
@@ -4093,10 +4093,10 @@
         <v>87.39999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>87.23</v>
+        <v>88.73</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
@@ -4132,10 +4132,10 @@
         <v>87.84999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>86.88250000000001</v>
+        <v>88.38250000000001</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -4171,10 +4171,10 @@
         <v>87.75</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>86.6875</v>
+        <v>88.1875</v>
       </c>
       <c r="J11" t="n">
         <v>10</v>
@@ -4210,10 +4210,10 @@
         <v>86.65000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>85.64250000000001</v>
+        <v>87.14250000000001</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
@@ -4249,10 +4249,10 @@
         <v>84.95</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>84.3275</v>
+        <v>85.8275</v>
       </c>
       <c r="J13" t="n">
         <v>12</v>
@@ -4288,10 +4288,10 @@
         <v>84.45</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>83.55249999999999</v>
+        <v>85.05249999999999</v>
       </c>
       <c r="J14" t="n">
         <v>13</v>
@@ -4327,10 +4327,10 @@
         <v>83.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>82.515</v>
+        <v>84.015</v>
       </c>
       <c r="J15" t="n">
         <v>14</v>
@@ -4366,10 +4366,10 @@
         <v>83.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>82.48500000000001</v>
+        <v>83.98500000000001</v>
       </c>
       <c r="J16" t="n">
         <v>15</v>
@@ -4405,10 +4405,10 @@
         <v>82.80000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>81.41000000000001</v>
+        <v>82.91000000000001</v>
       </c>
       <c r="J17" t="n">
         <v>16</v>
@@ -4444,10 +4444,10 @@
         <v>82.19999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>81.28999999999999</v>
+        <v>82.78999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>17</v>
@@ -4483,10 +4483,10 @@
         <v>83.30000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>81.08500000000001</v>
+        <v>82.58500000000001</v>
       </c>
       <c r="J19" t="n">
         <v>18</v>
@@ -4522,10 +4522,10 @@
         <v>83.05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>80.82250000000002</v>
+        <v>82.32250000000002</v>
       </c>
       <c r="J20" t="n">
         <v>19</v>
@@ -4561,10 +4561,10 @@
         <v>82.10000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>79.845</v>
+        <v>81.345</v>
       </c>
       <c r="J21" t="n">
         <v>20</v>
@@ -4600,10 +4600,10 @@
         <v>82.25000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>79.7625</v>
+        <v>81.2625</v>
       </c>
       <c r="J22" t="n">
         <v>21</v>
@@ -4639,10 +4639,10 @@
         <v>81.40000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>78.83</v>
+        <v>80.33</v>
       </c>
       <c r="J23" t="n">
         <v>22</v>
@@ -4678,10 +4678,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>78.545</v>
+        <v>80.045</v>
       </c>
       <c r="J24" t="n">
         <v>23</v>
@@ -4717,10 +4717,10 @@
         <v>80.45</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>77.70250000000001</v>
+        <v>79.20250000000001</v>
       </c>
       <c r="J25" t="n">
         <v>24</v>
@@ -4756,10 +4756,10 @@
         <v>80.5</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>77.575</v>
+        <v>79.075</v>
       </c>
       <c r="J26" t="n">
         <v>25</v>
@@ -4795,10 +4795,10 @@
         <v>80.65000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>77.0925</v>
+        <v>78.5925</v>
       </c>
       <c r="J27" t="n">
         <v>26</v>
@@ -4834,10 +4834,10 @@
         <v>80.25</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>76.7625</v>
+        <v>78.2625</v>
       </c>
       <c r="J28" t="n">
         <v>27</v>
@@ -4873,10 +4873,10 @@
         <v>80.75</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>76.28750000000001</v>
+        <v>77.78750000000001</v>
       </c>
       <c r="J29" t="n">
         <v>28</v>
@@ -4912,10 +4912,10 @@
         <v>79.5</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>75.875</v>
+        <v>77.375</v>
       </c>
       <c r="J30" t="n">
         <v>29</v>
@@ -4951,10 +4951,10 @@
         <v>79.10000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>74.995</v>
+        <v>76.495</v>
       </c>
       <c r="J31" t="n">
         <v>30</v>
@@ -4990,10 +4990,10 @@
         <v>78.40000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>74.53</v>
+        <v>76.03</v>
       </c>
       <c r="J32" t="n">
         <v>31</v>
@@ -5029,10 +5029,10 @@
         <v>78.7</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>74.11499999999999</v>
+        <v>75.61499999999999</v>
       </c>
       <c r="J33" t="n">
         <v>32</v>
@@ -5068,10 +5068,10 @@
         <v>78.75</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>73.9875</v>
+        <v>75.4875</v>
       </c>
       <c r="J34" t="n">
         <v>33</v>
@@ -5107,10 +5107,10 @@
         <v>78.34999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>73.1075</v>
+        <v>74.6075</v>
       </c>
       <c r="J35" t="n">
         <v>34</v>
@@ -5146,10 +5146,10 @@
         <v>77.5</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>72.875</v>
+        <v>74.375</v>
       </c>
       <c r="J36" t="n">
         <v>35</v>
@@ -5185,10 +5185,10 @@
         <v>77.5</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>72.175</v>
+        <v>73.675</v>
       </c>
       <c r="J37" t="n">
         <v>36</v>
@@ -5224,10 +5224,10 @@
         <v>76.55000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>71.59750000000001</v>
+        <v>73.09750000000001</v>
       </c>
       <c r="J38" t="n">
         <v>37</v>
@@ -5263,10 +5263,10 @@
         <v>77</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>71.25</v>
+        <v>72.75</v>
       </c>
       <c r="J39" t="n">
         <v>38</v>
@@ -5302,10 +5302,10 @@
         <v>77.10000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>71.14500000000001</v>
+        <v>72.64500000000001</v>
       </c>
       <c r="J40" t="n">
         <v>39</v>
@@ -5341,10 +5341,10 @@
         <v>76.55</v>
       </c>
       <c r="H41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>70.3475</v>
+        <v>71.8475</v>
       </c>
       <c r="J41" t="n">
         <v>40</v>
@@ -5380,10 +5380,10 @@
         <v>75.95</v>
       </c>
       <c r="H42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>69.92749999999999</v>
+        <v>71.42749999999999</v>
       </c>
       <c r="J42" t="n">
         <v>41</v>
@@ -5419,10 +5419,10 @@
         <v>75.25</v>
       </c>
       <c r="H43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>69.0625</v>
+        <v>70.5625</v>
       </c>
       <c r="J43" t="n">
         <v>42</v>
@@ -5458,10 +5458,10 @@
         <v>75.25</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>68.91250000000001</v>
+        <v>70.41250000000001</v>
       </c>
       <c r="J44" t="n">
         <v>43</v>
@@ -5497,10 +5497,10 @@
         <v>76.2</v>
       </c>
       <c r="H45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>68.64</v>
+        <v>70.14</v>
       </c>
       <c r="J45" t="n">
         <v>44</v>
@@ -5536,10 +5536,10 @@
         <v>75.2</v>
       </c>
       <c r="H46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>68.34</v>
+        <v>69.84</v>
       </c>
       <c r="J46" t="n">
         <v>45</v>
@@ -5575,10 +5575,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>67.81999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>46</v>
@@ -5614,10 +5614,10 @@
         <v>75.95</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>67.12750000000001</v>
+        <v>68.62750000000001</v>
       </c>
       <c r="J48" t="n">
         <v>47</v>
@@ -5653,10 +5653,10 @@
         <v>74.34999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>67.1075</v>
+        <v>68.6075</v>
       </c>
       <c r="J49" t="n">
         <v>48</v>
@@ -5692,10 +5692,10 @@
         <v>75.05</v>
       </c>
       <c r="H50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>66.8725</v>
+        <v>68.3725</v>
       </c>
       <c r="J50" t="n">
         <v>49</v>
@@ -5731,10 +5731,10 @@
         <v>74.65000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>65.8425</v>
+        <v>67.3425</v>
       </c>
       <c r="J51" t="n">
         <v>50</v>
@@ -5770,10 +5770,10 @@
         <v>74.25</v>
       </c>
       <c r="H52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>65.8125</v>
+        <v>67.3125</v>
       </c>
       <c r="J52" t="n">
         <v>51</v>
@@ -5809,10 +5809,10 @@
         <v>74.7</v>
       </c>
       <c r="H53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>65.16500000000001</v>
+        <v>66.66500000000001</v>
       </c>
       <c r="J53" t="n">
         <v>52</v>
@@ -5848,10 +5848,10 @@
         <v>75.60000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>64.87</v>
+        <v>66.37</v>
       </c>
       <c r="J54" t="n">
         <v>53</v>
@@ -5887,10 +5887,10 @@
         <v>72.75</v>
       </c>
       <c r="H55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>64.4375</v>
+        <v>65.9375</v>
       </c>
       <c r="J55" t="n">
         <v>54</v>
@@ -5926,10 +5926,10 @@
         <v>72.94999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>63.8275</v>
+        <v>65.3275</v>
       </c>
       <c r="J56" t="n">
         <v>55</v>
@@ -5965,10 +5965,10 @@
         <v>74.25</v>
       </c>
       <c r="H57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>63.71250000000001</v>
+        <v>65.21250000000001</v>
       </c>
       <c r="J57" t="n">
         <v>56</v>
@@ -6004,10 +6004,10 @@
         <v>74.15000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>63.51750000000001</v>
+        <v>65.01750000000001</v>
       </c>
       <c r="J58" t="n">
         <v>57</v>
@@ -6043,10 +6043,10 @@
         <v>73.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>62.70500000000001</v>
+        <v>64.20500000000001</v>
       </c>
       <c r="J59" t="n">
         <v>58</v>
@@ -6082,10 +6082,10 @@
         <v>74.40000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>62.38000000000001</v>
+        <v>63.88000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>59</v>
@@ -6121,10 +6121,10 @@
         <v>71.8</v>
       </c>
       <c r="H61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>61.91</v>
+        <v>63.41</v>
       </c>
       <c r="J61" t="n">
         <v>60</v>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-22 16:24</t>
+          <t>2026-06-29 15:26</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.9</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.7</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>72.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>11.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>74.7</v>
+        <v>78.3</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>70.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>8.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>76.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>12.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>94.5</v>
+        <v>100.1</v>
       </c>
       <c r="C6" t="n">
-        <v>76.3</v>
+        <v>75.3</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>13.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.8</v>
+        <v>100.4</v>
       </c>
       <c r="C7" t="n">
-        <v>78.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>12.2</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>101.8</v>
+        <v>103.1</v>
       </c>
       <c r="C8" t="n">
-        <v>78.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>8.800000000000001</v>
+        <v>14.4</v>
       </c>
     </row>
   </sheetData>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-29 15:26</t>
+          <t>2026-07-06 14:54</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.3</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>97.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>97.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="C3" t="n">
-        <v>78.3</v>
+        <v>76.5</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>10.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>97.90000000000001</v>
+        <v>101.9</v>
       </c>
       <c r="C4" t="n">
-        <v>75.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>11.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97.90000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="C5" t="n">
-        <v>75.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100.1</v>
+        <v>102.8</v>
       </c>
       <c r="C6" t="n">
-        <v>75.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>9.300000000000001</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100.4</v>
+        <v>102.3</v>
       </c>
       <c r="C7" t="n">
-        <v>77.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>10.4</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>103.1</v>
+        <v>100.2</v>
       </c>
       <c r="C8" t="n">
-        <v>79.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>14.4</v>
+        <v>17.1</v>
       </c>
     </row>
   </sheetData>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-06 14:54</t>
+          <t>2026-07-13 13:59</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.1</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.3</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96.5</v>
+        <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>75.7</v>
+        <v>73.8</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95.3</v>
+        <v>86.2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>101.9</v>
+        <v>94.2</v>
       </c>
       <c r="C4" t="n">
-        <v>77.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>13.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100.1</v>
+        <v>96.7</v>
       </c>
       <c r="C5" t="n">
         <v>77.2</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>10.9</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102.8</v>
+        <v>100.6</v>
       </c>
       <c r="C6" t="n">
-        <v>80.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102.3</v>
+        <v>98.7</v>
       </c>
       <c r="C7" t="n">
-        <v>83.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>12.3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100.2</v>
+        <v>99.2</v>
       </c>
       <c r="C8" t="n">
-        <v>81.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>17.1</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-13 13:59</t>
+          <t>2026-07-20 13:44</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.4</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n">
-        <v>73.8</v>
+        <v>75.8</v>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>73.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>10.1</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>94.2</v>
+        <v>98.5</v>
       </c>
       <c r="C4" t="n">
-        <v>75.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>8.199999999999999</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96.7</v>
+        <v>95.2</v>
       </c>
       <c r="C5" t="n">
-        <v>77.2</v>
+        <v>80.3</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100.6</v>
+        <v>87.3</v>
       </c>
       <c r="C6" t="n">
-        <v>77.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>10.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.7</v>
+        <v>80.5</v>
       </c>
       <c r="C7" t="n">
-        <v>77.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>99.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>79.8</v>
+        <v>73.8</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>12.5</v>
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20 13:44</t>
+          <t>2026-07-27 14:07</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.4</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>75.8</v>
+        <v>76.7</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95.40000000000001</v>
+        <v>103.2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>98.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>78.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>80.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>75.3</v>
+        <v>76.7</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>74.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="C8" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>9.9</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-27 14:07</t>
+          <t>2026-08-03 14:11</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>97.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>76.7</v>
+        <v>74.2</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>77.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>13.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>80.7</v>
+        <v>74.7</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="C5" t="n">
-        <v>75.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>99.90000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>76.7</v>
+        <v>76.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>79.2</v>
+        <v>75.3</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>74.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>7.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/golf_model.xlsx
+++ b/golf_model.xlsx
@@ -443,7 +443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03 14:11</t>
+          <t>2026-08-10 12:40</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="10">
@@ -3594,134 +3594,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>74.2</v>
+        <v>75.8</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>94.90000000000001</v>
+        <v>100.8</v>
       </c>
       <c r="C4" t="n">
-        <v>74.7</v>
+        <v>81.2</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.8</v>
+        <v>103.5</v>
       </c>
       <c r="C5" t="n">
-        <v>75.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>9.4</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>96.90000000000001</v>
+        <v>102.4</v>
       </c>
       <c r="C6" t="n">
-        <v>76.2</v>
+        <v>80.8</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>11.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>104.2</v>
       </c>
       <c r="C7" t="n">
-        <v>75.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98.90000000000001</v>
+        <v>102.2</v>
       </c>
       <c r="C8" t="n">
-        <v>76.8</v>
+        <v>79.2</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
